--- a/products/store_b/out/05_Debt_Payoff_Planner.xlsx
+++ b/products/store_b/out/05_Debt_Payoff_Planner.xlsx
@@ -1137,11 +1137,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="21113035"/>
-        <c:axId val="41119000"/>
+        <c:axId val="85670230"/>
+        <c:axId val="29678596"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="21113035"/>
+        <c:axId val="85670230"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1173,7 +1173,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41119000"/>
+        <c:crossAx val="29678596"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1181,7 +1181,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41119000"/>
+        <c:axId val="29678596"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1223,7 +1223,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21113035"/>
+        <c:crossAx val="85670230"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1421,11 +1421,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="82225911"/>
-        <c:axId val="82978593"/>
+        <c:axId val="89579787"/>
+        <c:axId val="59210954"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="82225911"/>
+        <c:axId val="89579787"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1457,7 +1457,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82978593"/>
+        <c:crossAx val="59210954"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1465,7 +1465,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82978593"/>
+        <c:axId val="59210954"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1507,7 +1507,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82225911"/>
+        <c:crossAx val="89579787"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
